--- a/results/andar_할인율모니터링_20261031.xlsx
+++ b/results/andar_할인율모니터링_20261031.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -533,12 +533,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>563</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>563</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>563</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3,099</t>
+          <t>3,101</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3,099</t>
+          <t>3,101</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10,245</t>
+          <t>10,247</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1385,42 +1385,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12487&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=19330&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ENTBG-18</t>
+          <t>EPTSC-12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>시티 플로우 빅 숄더백</t>
+          <t>소프트 니트 기모 오버 니삭스</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1469,37 +1469,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18948&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18772&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EPTCP-04</t>
+          <t>EPTFR-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>라이트 에어 러닝 캡</t>
+          <t>폼롤러</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>59,000</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>49,000</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>39,000</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1511,163 +1511,163 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12511&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18772&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ENTSO-03</t>
+          <t>EPTFR-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>안다르 이지무브 화이트</t>
+          <t>폼롤러</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>129,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>62,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12511&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>ENTSO-03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>필라테스 크루 삭스</t>
+          <t>안다르 이지무브 화이트</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>129,000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>62,000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EPTET-01</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>언더웨어 파우치</t>
+          <t>필라테스 크루 삭스</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EPTET-01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>언더웨어 파우치</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3,281</t>
+          <t>383</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1679,42 +1679,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18948&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EPTCP-04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>라이트 에어 러닝 캡</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3,281</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -1763,289 +1763,289 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ENTSC-24</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>웜 슬릿 레그 워머</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>3,281</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EOTBG-23</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백 M</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>3,281</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18854&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EPTBG-10</t>
+          <t>EOTBG-23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>미니 크레센트 듀얼백</t>
+          <t>안다르 실버 리유저블백 M</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>421</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16649&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EPTBG-02</t>
+          <t>ENTSC-24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>서밋 유틸리티 백팩</t>
+          <t>웜 슬릿 레그 워머</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18854&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EPTBG-10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>필라테스 토삭스</t>
+          <t>미니 크레센트 듀얼백</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ENTSO-02</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (우먼즈)</t>
+          <t>[2ea] 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1,079</t>
+          <t>2,095</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (우먼즈)</t>
+          <t>필라테스 토삭스</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1,079</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2099,168 +2099,168 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>ENTSO-02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[2ea] 서포트 무릎 보호대</t>
+          <t>안다르 제트플라이 (우먼즈)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2,095</t>
+          <t>1,079</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 크루삭스</t>
+          <t>안다르 제트플라이 (우먼즈)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>1,079</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16649&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EOTBG-03</t>
+          <t>EPTBG-02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>데이 앤 트래블 숄더백</t>
+          <t>서밋 유틸리티 백팩</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 니삭스</t>
+          <t>논슬립 퍼포먼스 크루삭스</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>686</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -2351,37 +2351,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EOTBG-03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>레그 미들 워머</t>
+          <t>데이 앤 트래블 숄더백</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2393,79 +2393,79 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EPTBG-07</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>멀티 포켓 파우치</t>
+          <t>논슬립 퍼포먼스 니삭스</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>767</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EPTBG-07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (맨즈)</t>
+          <t>멀티 포켓 파우치</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2477,168 +2477,168 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 풀 토삭스</t>
+          <t>안다르 제트플라이 (맨즈)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>704</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EOTBG-13</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>멀티 포켓 숄더 앤 크로스백</t>
+          <t>맨즈 논슬립 풀 토삭스</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18768&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EPTBG-08</t>
+          <t>EOTFB-01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>데일리 캐리온 쇼퍼백</t>
+          <t>에어쿨링 와이드 헤드밴드</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2,578</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EOTFB-01</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>에어쿨링 와이드 헤드밴드</t>
+          <t>레그 미들 워머</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2,577</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -2687,168 +2687,168 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18768&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EPTBG-08</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[1&amp;1] 올데이 기모 삭스</t>
+          <t>데일리 캐리온 쇼퍼백</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EMTSC-01</t>
+          <t>EOTBG-10</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>링글 크루 삭스</t>
+          <t>에어플라이 투웨이 프리런 백 3.0</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5,500</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1,364</t>
+          <t>1,177</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EJFST-02</t>
+          <t>EOTBG-13</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>릴렉스 요가링</t>
+          <t>멀티 포켓 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>6,682</t>
+          <t>436</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EOTBG-10</t>
+          <t>EJFST-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>에어플라이 투웨이 프리런 백 3.0</t>
+          <t>릴렉스 요가링</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1,176</t>
+          <t>6,682</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -2897,37 +2897,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18767&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EPTBG-06</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 스퀘어 크로스백</t>
+          <t>[1&amp;1] 올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2939,101 +2939,101 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EOTSC-13</t>
+          <t>EOTMK-01</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>테이핑 러닝 삭스</t>
+          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>1,147</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=19339&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EPTCP-05</t>
+          <t>EOTSC-13</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>히트 런 이어플랩 캡 2.0</t>
+          <t>테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18767&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ENTBG-13</t>
+          <t>EPTBG-06</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>데일리 스퀘어백</t>
+          <t>컴팩트 포켓 스퀘어 크로스백</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3065,37 +3065,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EPTBG-03</t>
+          <t>EMTSC-01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 크로스백</t>
+          <t>링글 크루 삭스</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>5,500</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>1,364</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3107,27 +3107,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=19339&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EOTMK-01</t>
+          <t>EPTCP-05</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
+          <t>히트 런 이어플랩 캡 2.0</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3137,29 +3137,29 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1,147</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EOTCP-01</t>
+          <t>ENTBG-13</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>올라운드 버킷햇</t>
+          <t>데일리 스퀘어백</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3169,59 +3169,59 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>56,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ENTMT-01</t>
+          <t>EPTBG-03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>레스트 인 마블 요가매트 (4mm)</t>
+          <t>컴팩트 포켓 크로스백</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>172</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3233,79 +3233,79 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18765&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12487&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EPTSC-11</t>
+          <t>ENTBG-18</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>데일리 쿠션 크루 삭스</t>
+          <t>시티 플로우 빅 숄더백</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EOTBG-20</t>
+          <t>ENTMT-01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>클라우드 스트링 쇼퍼백</t>
+          <t>레스트 인 마블 요가매트 (4mm)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3317,22 +3317,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18765&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EPTSC-11</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>데일리 쿠션 크루 삭스</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3342,76 +3342,76 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EOTBG-20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[2ea] 하이 서포트 무릎 보호대</t>
+          <t>클라우드 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EPTET-02</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>언더웨어 세탁망</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3421,64 +3421,64 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EOTBG-21</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>데일리 라운드백</t>
+          <t>[2ea] 하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>762</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>576</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3527,247 +3527,247 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18772&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EPTFR-01</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>폼롤러</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18772&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EPTFR-02</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>폼롤러</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EPTET-02</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>언더웨어 세탁망</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EOTGL-04</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>논슬립 스킨 요기 글러브</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EOTGL-04</t>
+          <t>ENTBG-05</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>논슬립 스킨 요기 글러브</t>
+          <t>미니 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>5,207</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EOTBG-21</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
+          <t>데일리 라운드백</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3779,79 +3779,79 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ENTBG-05</t>
+          <t>EMTBG-12</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>미니 숄더 앤 크로스백</t>
+          <t>데일리 쇼퍼백</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>5,207</t>
+          <t>1,439</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EOTBG-15</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>폴더블 짐백 2.0</t>
+          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>742</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3863,37 +3863,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EMTBG-12</t>
+          <t>EKPMT-03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>데일리 쇼퍼백</t>
+          <t>릴렉스 논슬립 요가 타월</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1,439</t>
+          <t>1,599</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3905,37 +3905,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EKPMT-03</t>
+          <t>EOTBG-15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>릴렉스 논슬립 요가 타월</t>
+          <t>폴더블 짐백 2.0</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1,599</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3947,42 +3947,42 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ENTBG-03</t>
+          <t>EMTRB-01</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>데일리 스트링 쇼퍼백</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1,409</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EMTRB-01</t>
+          <t>EMTRB-02</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1,408</t>
+          <t>1,409</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EMTRB-02</t>
+          <t>EMTRB-03</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1,408</t>
+          <t>1,409</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4073,37 +4073,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EMTRB-03</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1,408</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4115,37 +4115,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EOTBG-14</t>
+          <t>ENTBG-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>폴더블 캐리백 2.0</t>
+          <t>데일리 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>754</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4199,22 +4199,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EOTSC-06</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>필라테스 앵클 삭스</t>
+          <t>서포트 쿠션 러닝 삭스</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4224,59 +4224,59 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>797</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=19340&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18759&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EPTCP-07</t>
+          <t>EPTMB-01</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>웜 패딩 버킷햇</t>
+          <t>마사지 싱글볼</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -4325,106 +4325,106 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=19340&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EOTSC-06</t>
+          <t>EPTCP-07</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>서포트 쿠션 러닝 삭스</t>
+          <t>웜 패딩 버킷햇</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EOTBG-12</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>[1&amp;1] 램스울 크루 삭스</t>
+          <t>프리런 벨크로 러닝 벨트</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>[1ea] 서포트 발목 보호대</t>
+          <t>[1ea] 하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>762</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4451,121 +4451,121 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18759&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EPTMB-01</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>마사지 싱글볼</t>
+          <t>[1&amp;1] 램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>887</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>ENTSC-20</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[1ea] 하이 서포트 무릎 보호대</t>
+          <t>시그니처 로고 크루 삭스</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>633</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EOTBG-12</t>
+          <t>EKPMB-01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>프리런 벨크로 러닝 벨트</t>
+          <t>릴렉스 웨이트볼 0.5kg</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4577,37 +4577,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ENTSC-20</t>
+          <t>EOTBG-14</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>시그니처 로고 크루 삭스</t>
+          <t>폴더블 캐리백 2.0</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4619,79 +4619,79 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 토삭스</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4,150</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4703,79 +4703,79 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t>12,900</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>10,900</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>4,150</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>[1ea] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4787,84 +4787,84 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>321</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EMTSV-06</t>
+          <t>ENTSC-08</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>에어쿨링 손목 보호대</t>
+          <t>[5 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>81,000</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1,125</t>
+          <t>859</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -4913,37 +4913,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EOTBG-17</t>
+          <t>EPTSV-03</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3 in 1 캐리온 더플백</t>
+          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4955,84 +4955,84 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EPTSV-03</t>
+          <t>EMTSV-06</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
+          <t>에어쿨링 손목 보호대</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1,125</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EKPRB-04</t>
+          <t>EOTBG-17</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
+          <t>3 in 1 캐리온 더플백</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>109,000</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -5081,163 +5081,163 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EKPRB-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
+          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18760&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EPTMB-02</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>마사지 듀얼볼</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>15,900</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>12,900</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>8,900</t>
-        </is>
-      </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EOTSV-03</t>
+          <t>ENTMU-01</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[1ea] 서포트 허리 보호대</t>
+          <t>소프트 니트 머플러</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>499</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ENTMU-01</t>
+          <t>EMTSC-29</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>소프트 니트 머플러</t>
+          <t>니트 루즈 삭스</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5249,37 +5249,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ENTSC-08</t>
+          <t>EOTGL-03</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[5 SET] 에어컴피 크루 삭스</t>
+          <t>소프트 니트 플립 글러브</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>81,000</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5291,37 +5291,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EMTSC-29</t>
+          <t>ENTFB-05</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>니트 루즈 삭스</t>
+          <t>소프트 니트 헤드밴드</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5333,17 +5333,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ENTFB-05</t>
+          <t>EOTSC-12</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>소프트 니트 헤드밴드</t>
+          <t>소프트 니트 기모 니삭스</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5353,259 +5353,259 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EOTGL-03</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>소프트 니트 플립 글러브</t>
+          <t>[2ea] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=19330&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EPTSC-12</t>
+          <t>EOTSV-03</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 오버 니삭스</t>
+          <t>[1ea] 서포트 허리 보호대</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EOTCP-06</t>
+          <t>EMTET-02</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>소프트 니트 버킷햇</t>
+          <t>소프트 쿠셔닝 훌라후프</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>681</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EOTSC-12</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 니삭스</t>
+          <t>라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=19352&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EPTCP-06</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>[2ea] 서포트 발목 보호대</t>
+          <t>와플 니트 비니</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EMTET-02</t>
+          <t>ENTBG-14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>소프트 쿠셔닝 훌라후프</t>
+          <t>웨이브 패딩 파우치</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5615,49 +5615,49 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18760&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EPTMB-02</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>마사지 듀얼볼</t>
+          <t>논슬립 스킨 하프 토삭스</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5669,205 +5669,205 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=19352&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EPTCP-06</t>
+          <t>EOTSC-10</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>와플 니트 비니</t>
+          <t>시그니처 로고 맨즈 크루 삭스</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ENTBG-14</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>웨이브 패딩 파우치</t>
+          <t>[1&amp;1] 데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>ENTFB-01</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>라이트 러닝 베스트</t>
+          <t>에어쿨링 라인 스크런치</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>821</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EKPRB-05</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>논슬립 스킨 하프 토삭스</t>
+          <t>릴렉스 4레벨 힙 밴드</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EOTSC-10</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>시그니처 로고 맨즈 크루 삭스</t>
+          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>398</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5879,37 +5879,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>[1&amp;1] 데일리 루즈 삭스</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5921,42 +5921,42 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ENTFB-01</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>에어쿨링 라인 스크런치</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -6005,163 +6005,163 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EKPRB-05</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>릴렉스 4레벨 힙 밴드</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>EOTSC-04</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>올데이 수피마 스니커즈 삭스</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>4,500</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>450</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18773&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EPTBG-11</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>올데이 기모 삭스</t>
+          <t>안다르 실버 리유저블백 L</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6173,163 +6173,163 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18773&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EPTBG-11</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백 L</t>
+          <t>[2ea] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>607</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>[2ea] 서포트 팔꿈치 보호대</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>657</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EKPMB-01</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>릴렉스 웨이트볼 0.5kg</t>
+          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>35,600</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>605</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EOTSC-04</t>
+          <t>EPTCP-02</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>올데이 수피마 스니커즈 삭스</t>
+          <t>시그니처 로고 나일론 볼캡</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>33,000</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6341,121 +6341,121 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
+          <t>컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>35,600</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>컴프레션 러닝 니삭스</t>
+          <t>맨즈 라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EOTSC-05</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>맨즈 라이트 러닝 베스트</t>
+          <t>올데이 수피마 앵클 삭스</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>486</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6467,69 +6467,69 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EPTCP-02</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>시그니처 로고 나일론 볼캡</t>
+          <t>램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>33,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>369</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EOTSC-05</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>올데이 수피마 앵클 삭스</t>
+          <t>에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6539,49 +6539,49 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>576</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EOTSC-01</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>프레시 필드 니삭스</t>
+          <t>[2ea] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>164</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6593,27 +6593,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EOTSC-01</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>에어컴피 크루 삭스</t>
+          <t>프레시 필드 니삭스</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6623,91 +6623,91 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>램스울 크루 삭스</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EOTCP-02</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>[2ea] 하이 서포트 팔꿈치 보호대</t>
+          <t>데님 로고 볼캡</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6719,42 +6719,42 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>132</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
@@ -6803,121 +6803,121 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17387&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>맨즈 필라테스 크루 삭스</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17387&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>EOTBG-04</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 크루 삭스</t>
+          <t>데님 포켓 숄더백</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EOTBG-04</t>
+          <t>ENTBG-16</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>데님 포켓 숄더백</t>
+          <t>라이트 패딩 쇼퍼백</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
+          <t>69,000</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>59,000</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>59,000</t>
-        </is>
-      </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>635</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6929,37 +6929,37 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ENTBG-16</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>라이트 패딩 쇼퍼백</t>
+          <t>[1ea] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>164</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6971,22 +6971,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>[1ea] 하이 서포트 팔꿈치 보호대</t>
+          <t>[1ea] 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6996,17 +6996,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2,095</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>607</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7055,40 +7055,628 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EOTCP-02</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>데님 로고 볼캡</t>
+          <t>데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t>11,900</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>9,900</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>EOTBG-05</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>메쉬 포켓 비치백</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>49,000</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>49,000</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>EMTSC-28</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>리브드 셔링 루즈 삭스</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>EPTET-03</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>안다르 3단 양우산</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>29,000</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>29,000</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>EPTSC-07</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>맨즈 필라테스 앵클 삭스</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>13,900</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>11,900</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>EPTBG-05</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>안다르 시그니처 로고 에코백</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
           <t>39,000</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>28,000</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ENTET-02</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>릴렉스 소프트 웨이트바 2kg</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>37,000</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=15151&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>EOTBG-22</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>투포켓 로고 캔버스백</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>49,000</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>49,000</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ENTCP-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>와이드 셰이드 버킷햇</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>59,000</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>47,000</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>EOTCP-03</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>쿨 라운드 볼캡</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>45,000</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>32,000</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ENTSV-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>3D 쿨링 팔토시</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>14,900</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>14,900</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ENTSC-19</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>맨즈 논슬립 하프 토삭스</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>11,900</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=11208&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ENTSC-21</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>링글 오버 니삭스</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>13,900</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>13,900</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ENTSC-05</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>에어프레시 크루 삭스</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>17,000</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>EKPET-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>릴렉스 소프트 웨이트바 1kg</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>20,900</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
